--- a/artfynd/A 14173-2024 artfynd.xlsx
+++ b/artfynd/A 14173-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121690963</v>
+        <v>121692954</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>58034</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514423</v>
+        <v>514406</v>
       </c>
       <c r="R2" t="n">
-        <v>6584688</v>
+        <v>6584611</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692954</v>
+        <v>121690963</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>57726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514406</v>
+        <v>514423</v>
       </c>
       <c r="R3" t="n">
-        <v>6584611</v>
+        <v>6584688</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14173-2024 artfynd.xlsx
+++ b/artfynd/A 14173-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121692954</v>
+        <v>121690963</v>
       </c>
       <c r="B2" t="n">
-        <v>58034</v>
+        <v>57726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514406</v>
+        <v>514423</v>
       </c>
       <c r="R2" t="n">
-        <v>6584611</v>
+        <v>6584688</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121690963</v>
+        <v>121692954</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>58034</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514423</v>
+        <v>514406</v>
       </c>
       <c r="R3" t="n">
-        <v>6584688</v>
+        <v>6584611</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14173-2024 artfynd.xlsx
+++ b/artfynd/A 14173-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121690963</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>57734</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>121692954</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58042</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 14173-2024 artfynd.xlsx
+++ b/artfynd/A 14173-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121690963</v>
+        <v>121692954</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>58042</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514423</v>
+        <v>514406</v>
       </c>
       <c r="R2" t="n">
-        <v>6584688</v>
+        <v>6584611</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692954</v>
+        <v>121690963</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>57734</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514406</v>
+        <v>514423</v>
       </c>
       <c r="R3" t="n">
-        <v>6584611</v>
+        <v>6584688</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14173-2024 artfynd.xlsx
+++ b/artfynd/A 14173-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121692954</v>
       </c>
       <c r="B2" t="n">
-        <v>58042</v>
+        <v>58046</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>121690963</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
